--- a/Tech.xlsx
+++ b/Tech.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD04CF0-C52A-4803-94F6-4B0551FFE3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C3C846-9E05-4411-AF64-F921AEE11667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="4" xr2:uid="{99A4F583-0E14-4765-AB16-7E206A98D14D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{99A4F583-0E14-4765-AB16-7E206A98D14D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -112,6 +112,7 @@
     <externalReference r:id="rId95"/>
     <externalReference r:id="rId96"/>
     <externalReference r:id="rId97"/>
+    <externalReference r:id="rId98"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -134,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5037" uniqueCount="3149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5038" uniqueCount="3149">
   <si>
     <t>Name</t>
   </si>
@@ -10163,7 +10164,7 @@
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -10195,8 +10196,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -13690,6 +13689,45 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink89.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>251.74</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>283312.98862612003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>10259</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>81426</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -35761,7 +35799,7 @@
       <c r="H3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="16" t="s">
         <v>2584</v>
       </c>
       <c r="J3" s="10" t="s">
@@ -35784,14 +35822,33 @@
       <c r="A4" s="5">
         <v>1</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="1" t="s">
         <v>2716</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" t="s">
         <v>2717</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" t="s">
         <v>3099</v>
+      </c>
+      <c r="E4">
+        <f>+[89]Main!$I$2</f>
+        <v>251.74</v>
+      </c>
+      <c r="F4" s="4">
+        <f>+[89]Main!$I$4</f>
+        <v>283312.98862612003</v>
+      </c>
+      <c r="G4" s="4">
+        <f>+[89]Main!$I$6-[89]Main!$I$5</f>
+        <v>71167</v>
+      </c>
+      <c r="H4" s="4">
+        <f>+F4+G4</f>
+        <v>354479.98862612003</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>2587</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -35799,3173 +35856,3812 @@
         <f>+A4+1</f>
         <v>2</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" t="s">
         <v>2718</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" t="s">
         <v>2719</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" t="s">
         <v>3100</v>
       </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" ref="A6:A69" si="0">+A5+1</f>
         <v>3</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" t="s">
         <v>2720</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" t="s">
         <v>2721</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" t="s">
         <v>3099</v>
       </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" t="s">
         <v>2722</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" t="s">
         <v>2723</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" t="s">
         <v>3099</v>
       </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" t="s">
         <v>2724</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" t="s">
         <v>2725</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" t="s">
         <v>3101</v>
       </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" t="s">
         <v>2726</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" t="s">
         <v>2727</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" t="s">
         <v>3102</v>
       </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" t="s">
         <v>2728</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" t="s">
         <v>2729</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" t="s">
         <v>3103</v>
       </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" t="s">
         <v>2730</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" t="s">
         <v>2731</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" t="s">
         <v>3099</v>
       </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" t="s">
         <v>2732</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" t="s">
         <v>2733</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" t="s">
         <v>3099</v>
       </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" t="s">
         <v>2734</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" t="s">
         <v>2735</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" t="s">
         <v>3100</v>
       </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" t="s">
         <v>3146</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" t="s">
         <v>3147</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" t="s">
         <v>3102</v>
       </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" t="s">
         <v>2736</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" t="s">
         <v>2737</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" t="s">
         <v>3102</v>
       </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" t="s">
         <v>2738</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" t="s">
         <v>2739</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" t="s">
         <v>3104</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" t="s">
         <v>2740</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" t="s">
         <v>2741</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" t="s">
         <v>3105</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" t="s">
         <v>2742</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" t="s">
         <v>2743</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" t="s">
         <v>3106</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" t="s">
         <v>2744</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" t="s">
         <v>2745</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" t="s">
         <v>2746</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" t="s">
         <v>2747</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" t="s">
         <v>3107</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" t="s">
         <v>2748</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" t="s">
         <v>2749</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" t="s">
         <v>3108</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" t="s">
         <v>2750</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" t="s">
         <v>2751</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" t="s">
         <v>3109</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" t="s">
         <v>2752</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" t="s">
         <v>2753</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" t="s">
         <v>2754</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" t="s">
         <v>2755</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" t="s">
         <v>3110</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" t="s">
         <v>2756</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" t="s">
         <v>2757</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" t="s">
         <v>3111</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" t="s">
         <v>2758</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" t="s">
         <v>2759</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" t="s">
         <v>3112</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" t="s">
         <v>2760</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" t="s">
         <v>2761</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" t="s">
         <v>3113</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" t="s">
         <v>2762</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" t="s">
         <v>2763</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" t="s">
         <v>3100</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" t="s">
         <v>2764</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" t="s">
         <v>2765</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" t="s">
         <v>3114</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" t="s">
         <v>2766</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" t="s">
         <v>2767</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" t="s">
         <v>3114</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" t="s">
         <v>2768</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" t="s">
         <v>2769</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" t="s">
         <v>3115</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" t="s">
         <v>2770</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" t="s">
         <v>2771</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" t="s">
         <v>3100</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" t="s">
         <v>2772</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" t="s">
         <v>2773</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" t="s">
         <v>3109</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" t="s">
         <v>2774</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="C34" t="s">
         <v>2775</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" t="s">
         <v>3116</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" t="s">
         <v>2776</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" t="s">
         <v>2777</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" t="s">
         <v>3113</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" t="s">
         <v>2778</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" t="s">
         <v>2779</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="D36" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" t="s">
         <v>2780</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" t="s">
         <v>2780</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" t="s">
         <v>3116</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" t="s">
         <v>2781</v>
       </c>
-      <c r="C38" s="21" t="s">
+      <c r="C38" t="s">
         <v>2782</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="D38" t="s">
         <v>3117</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" t="s">
         <v>2783</v>
       </c>
-      <c r="C39" s="21" t="s">
+      <c r="C39" t="s">
         <v>2784</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="D39" t="s">
         <v>3118</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" t="s">
         <v>2785</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" t="s">
         <v>2786</v>
       </c>
-      <c r="D40" s="22" t="s">
+      <c r="D40" t="s">
         <v>3119</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" t="s">
         <v>2787</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" t="s">
         <v>2788</v>
       </c>
-      <c r="D41" s="22" t="s">
+      <c r="D41" t="s">
         <v>3116</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" t="s">
         <v>2789</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" t="s">
         <v>2790</v>
       </c>
-      <c r="D42" s="22" t="s">
+      <c r="D42" t="s">
         <v>3120</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" t="s">
         <v>2791</v>
       </c>
-      <c r="C43" s="21" t="s">
+      <c r="C43" t="s">
         <v>498</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" t="s">
         <v>2792</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="C44" t="s">
         <v>2793</v>
       </c>
-      <c r="D44" s="22" t="s">
+      <c r="D44" t="s">
         <v>3121</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" t="s">
         <v>2794</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="C45" t="s">
         <v>2795</v>
       </c>
-      <c r="D45" s="22" t="s">
+      <c r="D45" t="s">
         <v>3121</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B46" s="21" t="s">
+      <c r="B46" t="s">
         <v>2796</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C46" t="s">
         <v>2797</v>
       </c>
-      <c r="D46" s="22" t="s">
+      <c r="D46" t="s">
         <v>3122</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" t="s">
         <v>2798</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="C47" t="s">
         <v>2799</v>
       </c>
-      <c r="D47" s="22" t="s">
+      <c r="D47" t="s">
         <v>3100</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B48" s="21" t="s">
+      <c r="B48" t="s">
         <v>2800</v>
       </c>
-      <c r="C48" s="21" t="s">
+      <c r="C48" t="s">
         <v>2801</v>
       </c>
-      <c r="D48" s="22" t="s">
+      <c r="D48" t="s">
         <v>3105</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B49" s="21" t="s">
+      <c r="B49" t="s">
         <v>2802</v>
       </c>
-      <c r="C49" s="21" t="s">
+      <c r="C49" t="s">
         <v>2803</v>
       </c>
-      <c r="D49" s="22" t="s">
+      <c r="D49" t="s">
         <v>3108</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="B50" t="s">
         <v>2804</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C50" t="s">
         <v>2805</v>
       </c>
-      <c r="D50" s="22" t="s">
+      <c r="D50" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B51" s="21" t="s">
+      <c r="B51" t="s">
         <v>2806</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" t="s">
         <v>2807</v>
       </c>
-      <c r="D51" s="22" t="s">
+      <c r="D51" t="s">
         <v>3115</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B52" s="21" t="s">
+      <c r="B52" t="s">
         <v>2808</v>
       </c>
-      <c r="C52" s="21" t="s">
+      <c r="C52" t="s">
         <v>2809</v>
       </c>
-      <c r="D52" s="22" t="s">
+      <c r="D52" t="s">
         <v>3122</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B53" s="21" t="s">
+      <c r="B53" t="s">
         <v>2810</v>
       </c>
-      <c r="C53" s="21" t="s">
+      <c r="C53" t="s">
         <v>2811</v>
       </c>
-      <c r="D53" s="22" t="s">
+      <c r="D53" t="s">
         <v>3114</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B54" s="21" t="s">
+      <c r="B54" t="s">
         <v>2812</v>
       </c>
-      <c r="C54" s="21" t="s">
+      <c r="C54" t="s">
         <v>2813</v>
       </c>
-      <c r="D54" s="22" t="s">
+      <c r="D54" t="s">
         <v>3123</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B55" s="21" t="s">
+      <c r="B55" t="s">
         <v>2814</v>
       </c>
-      <c r="C55" s="21" t="s">
+      <c r="C55" t="s">
         <v>2815</v>
       </c>
-      <c r="D55" s="22" t="s">
+      <c r="D55" t="s">
         <v>3124</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B56" s="21" t="s">
+      <c r="B56" t="s">
         <v>2816</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="C56" t="s">
         <v>2817</v>
       </c>
-      <c r="D56" s="22" t="s">
+      <c r="D56" t="s">
         <v>3109</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B57" s="21" t="s">
+      <c r="B57" t="s">
         <v>2818</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C57" t="s">
         <v>2819</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D57" t="s">
         <v>3123</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B58" s="21" t="s">
+      <c r="B58" t="s">
         <v>2820</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" t="s">
         <v>2821</v>
       </c>
-      <c r="D58" s="22" t="s">
+      <c r="D58" t="s">
         <v>3114</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="B59" t="s">
         <v>2822</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C59" t="s">
         <v>2823</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="D59" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B60" s="21" t="s">
+      <c r="B60" t="s">
         <v>2824</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="C60" t="s">
         <v>2825</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B61" s="21" t="s">
+      <c r="B61" t="s">
         <v>2826</v>
       </c>
-      <c r="C61" s="21" t="s">
+      <c r="C61" t="s">
         <v>2827</v>
       </c>
-      <c r="D61" s="22" t="s">
+      <c r="D61" t="s">
         <v>3112</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B62" s="21" t="s">
+      <c r="B62" t="s">
         <v>2828</v>
       </c>
-      <c r="C62" s="21" t="s">
+      <c r="C62" t="s">
         <v>2829</v>
       </c>
-      <c r="D62" s="22" t="s">
+      <c r="D62" t="s">
         <v>3125</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B63" s="21" t="s">
+      <c r="B63" t="s">
         <v>2830</v>
       </c>
-      <c r="C63" s="21" t="s">
+      <c r="C63" t="s">
         <v>2831</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D63" t="s">
         <v>3108</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B64" s="21" t="s">
+      <c r="B64" t="s">
         <v>2832</v>
       </c>
-      <c r="C64" s="21" t="s">
+      <c r="C64" t="s">
         <v>2833</v>
       </c>
-      <c r="D64" s="22" t="s">
+      <c r="D64" t="s">
         <v>3118</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B65" s="21" t="s">
+      <c r="B65" t="s">
         <v>2834</v>
       </c>
-      <c r="C65" s="21" t="s">
+      <c r="C65" t="s">
         <v>2835</v>
       </c>
-      <c r="D65" s="22" t="s">
+      <c r="D65" t="s">
         <v>3126</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B66" s="21" t="s">
+      <c r="B66" t="s">
         <v>2836</v>
       </c>
-      <c r="C66" s="21" t="s">
+      <c r="C66" t="s">
         <v>2837</v>
       </c>
-      <c r="D66" s="22" t="s">
+      <c r="D66" t="s">
         <v>3112</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B67" s="21" t="s">
+      <c r="B67" t="s">
         <v>2838</v>
       </c>
-      <c r="C67" s="21" t="s">
+      <c r="C67" t="s">
         <v>2839</v>
       </c>
-      <c r="D67" s="22" t="s">
+      <c r="D67" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B68" s="21" t="s">
+      <c r="B68" t="s">
         <v>2840</v>
       </c>
-      <c r="C68" s="21" t="s">
+      <c r="C68" t="s">
         <v>2841</v>
       </c>
-      <c r="D68" s="22" t="s">
+      <c r="D68" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B69" s="21" t="s">
+      <c r="B69" t="s">
         <v>2842</v>
       </c>
-      <c r="C69" s="21" t="s">
+      <c r="C69" t="s">
         <v>2843</v>
       </c>
-      <c r="D69" s="22" t="s">
+      <c r="D69" t="s">
         <v>3127</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <f t="shared" ref="A70:A133" si="1">+A69+1</f>
         <v>67</v>
       </c>
-      <c r="B70" s="21" t="s">
+      <c r="B70" t="s">
         <v>2844</v>
       </c>
-      <c r="C70" s="21" t="s">
+      <c r="C70" t="s">
         <v>2845</v>
       </c>
-      <c r="D70" s="22" t="s">
+      <c r="D70" t="s">
         <v>3126</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="B71" s="21" t="s">
+      <c r="B71" t="s">
         <v>2846</v>
       </c>
-      <c r="C71" s="21" t="s">
+      <c r="C71" t="s">
         <v>2847</v>
       </c>
-      <c r="D71" s="22" t="s">
+      <c r="D71" t="s">
         <v>3119</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="B72" s="21" t="s">
+      <c r="B72" t="s">
         <v>2848</v>
       </c>
-      <c r="C72" s="21" t="s">
+      <c r="C72" t="s">
         <v>2849</v>
       </c>
-      <c r="D72" s="22" t="s">
+      <c r="D72" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="B73" s="21" t="s">
+      <c r="B73" t="s">
         <v>2850</v>
       </c>
-      <c r="C73" s="21" t="s">
+      <c r="C73" t="s">
         <v>2851</v>
       </c>
-      <c r="D73" s="22" t="s">
+      <c r="D73" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-      <c r="B74" s="21" t="s">
+      <c r="B74" t="s">
         <v>2852</v>
       </c>
-      <c r="C74" s="21" t="s">
+      <c r="C74" t="s">
         <v>2853</v>
       </c>
-      <c r="D74" s="22" t="s">
+      <c r="D74" t="s">
         <v>3128</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="B75" s="21" t="s">
+      <c r="B75" t="s">
         <v>2854</v>
       </c>
-      <c r="C75" s="21" t="s">
+      <c r="C75" t="s">
         <v>2855</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="D75" t="s">
         <v>1642</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-      <c r="B76" s="21" t="s">
+      <c r="B76" t="s">
         <v>2856</v>
       </c>
-      <c r="C76" s="21" t="s">
+      <c r="C76" t="s">
         <v>2857</v>
       </c>
-      <c r="D76" s="22" t="s">
+      <c r="D76" t="s">
         <v>3129</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="B77" s="21" t="s">
+      <c r="B77" t="s">
         <v>2858</v>
       </c>
-      <c r="C77" s="21" t="s">
+      <c r="C77" t="s">
         <v>2859</v>
       </c>
-      <c r="D77" s="22" t="s">
+      <c r="D77" t="s">
         <v>3130</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="B78" s="21" t="s">
+      <c r="B78" t="s">
         <v>2860</v>
       </c>
-      <c r="C78" s="21" t="s">
+      <c r="C78" t="s">
         <v>2861</v>
       </c>
-      <c r="D78" s="22" t="s">
+      <c r="D78" t="s">
         <v>3126</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
-      <c r="B79" s="21" t="s">
+      <c r="B79" t="s">
         <v>2862</v>
       </c>
-      <c r="C79" s="21" t="s">
+      <c r="C79" t="s">
         <v>620</v>
       </c>
-      <c r="D79" s="22" t="s">
+      <c r="D79" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
-      <c r="B80" s="21" t="s">
+      <c r="B80" t="s">
         <v>2863</v>
       </c>
-      <c r="C80" s="21" t="s">
+      <c r="C80" t="s">
         <v>2864</v>
       </c>
-      <c r="D80" s="22" t="s">
+      <c r="D80" t="s">
         <v>3125</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
-      <c r="B81" s="21" t="s">
+      <c r="B81" t="s">
         <v>2865</v>
       </c>
-      <c r="C81" s="21" t="s">
+      <c r="C81" t="s">
         <v>2866</v>
       </c>
-      <c r="D81" s="22" t="s">
+      <c r="D81" t="s">
         <v>3116</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
-      <c r="B82" s="21" t="s">
+      <c r="B82" t="s">
         <v>2867</v>
       </c>
-      <c r="C82" s="21" t="s">
+      <c r="C82" t="s">
         <v>2868</v>
       </c>
-      <c r="D82" s="22" t="s">
+      <c r="D82" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="B83" s="21" t="s">
+      <c r="B83" t="s">
         <v>2869</v>
       </c>
-      <c r="C83" s="21" t="s">
+      <c r="C83" t="s">
         <v>2870</v>
       </c>
-      <c r="D83" s="22" t="s">
+      <c r="D83" t="s">
         <v>3125</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
-      <c r="B84" s="21" t="s">
+      <c r="B84" t="s">
         <v>2871</v>
       </c>
-      <c r="C84" s="21" t="s">
+      <c r="C84" t="s">
         <v>2872</v>
       </c>
-      <c r="D84" s="22" t="s">
+      <c r="D84" t="s">
         <v>3111</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
-      <c r="B85" s="21" t="s">
+      <c r="B85" t="s">
         <v>2873</v>
       </c>
-      <c r="C85" s="21" t="s">
+      <c r="C85" t="s">
         <v>2874</v>
       </c>
-      <c r="D85" s="22" t="s">
+      <c r="D85" t="s">
         <v>3131</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="B86" s="21" t="s">
+      <c r="B86" t="s">
         <v>2875</v>
       </c>
-      <c r="C86" s="21" t="s">
+      <c r="C86" t="s">
         <v>2876</v>
       </c>
-      <c r="D86" s="22" t="s">
+      <c r="D86" t="s">
         <v>3125</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="B87" s="21" t="s">
+      <c r="B87" t="s">
         <v>2877</v>
       </c>
-      <c r="C87" s="21" t="s">
+      <c r="C87" t="s">
         <v>2878</v>
       </c>
-      <c r="D87" s="22" t="s">
+      <c r="D87" t="s">
         <v>3132</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="B88" s="21" t="s">
+      <c r="B88" t="s">
         <v>695</v>
       </c>
-      <c r="C88" s="21" t="s">
+      <c r="C88" t="s">
         <v>696</v>
       </c>
-      <c r="D88" s="22" t="s">
+      <c r="D88" t="s">
         <v>3101</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="B89" s="21" t="s">
+      <c r="B89" t="s">
         <v>2879</v>
       </c>
-      <c r="C89" s="21" t="s">
+      <c r="C89" t="s">
         <v>2880</v>
       </c>
-      <c r="D89" s="22" t="s">
+      <c r="D89" t="s">
         <v>3109</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="B90" s="21" t="s">
+      <c r="B90" t="s">
         <v>2881</v>
       </c>
-      <c r="C90" s="21" t="s">
+      <c r="C90" t="s">
         <v>2882</v>
       </c>
-      <c r="D90" s="22" t="s">
+      <c r="D90" t="s">
         <v>3133</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="B91" s="21" t="s">
+      <c r="B91" t="s">
         <v>2883</v>
       </c>
-      <c r="C91" s="21" t="s">
+      <c r="C91" t="s">
         <v>2884</v>
       </c>
-      <c r="D91" s="22" t="s">
+      <c r="D91" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="B92" s="21" t="s">
+      <c r="B92" t="s">
         <v>2885</v>
       </c>
-      <c r="C92" s="21" t="s">
+      <c r="C92" t="s">
         <v>2886</v>
       </c>
-      <c r="D92" s="22" t="s">
+      <c r="D92" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="B93" s="21" t="s">
+      <c r="B93" t="s">
         <v>2887</v>
       </c>
-      <c r="C93" s="21" t="s">
+      <c r="C93" t="s">
         <v>2888</v>
       </c>
-      <c r="D93" s="22" t="s">
+      <c r="D93" t="s">
         <v>3119</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
-      <c r="B94" s="21" t="s">
+      <c r="B94" t="s">
         <v>2889</v>
       </c>
-      <c r="C94" s="21" t="s">
+      <c r="C94" t="s">
         <v>2890</v>
       </c>
-      <c r="D94" s="22" t="s">
+      <c r="D94" t="s">
         <v>3133</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="B95" s="21" t="s">
+      <c r="B95" t="s">
         <v>2891</v>
       </c>
-      <c r="C95" s="21" t="s">
+      <c r="C95" t="s">
         <v>2892</v>
       </c>
-      <c r="D95" s="22" t="s">
+      <c r="D95" t="s">
         <v>3134</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="B96" s="21" t="s">
+      <c r="B96" t="s">
         <v>2893</v>
       </c>
-      <c r="C96" s="21" t="s">
+      <c r="C96" t="s">
         <v>2894</v>
       </c>
-      <c r="D96" s="22" t="s">
+      <c r="D96" t="s">
         <v>3131</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-      <c r="B97" s="21" t="s">
+      <c r="B97" t="s">
         <v>644</v>
       </c>
-      <c r="C97" s="21" t="s">
+      <c r="C97" t="s">
         <v>645</v>
       </c>
-      <c r="D97" s="22" t="s">
+      <c r="D97" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-      <c r="B98" s="21" t="s">
+      <c r="B98" t="s">
         <v>2895</v>
       </c>
-      <c r="C98" s="21" t="s">
+      <c r="C98" t="s">
         <v>2896</v>
       </c>
-      <c r="D98" s="22" t="s">
+      <c r="D98" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="B99" s="21" t="s">
+      <c r="B99" t="s">
         <v>2897</v>
       </c>
-      <c r="C99" s="21" t="s">
+      <c r="C99" t="s">
         <v>2897</v>
       </c>
-      <c r="D99" s="22" t="s">
+      <c r="D99" t="s">
         <v>3120</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
-      <c r="B100" s="21" t="s">
+      <c r="B100" t="s">
         <v>2898</v>
       </c>
-      <c r="C100" s="21" t="s">
+      <c r="C100" t="s">
         <v>2899</v>
       </c>
-      <c r="D100" s="22" t="s">
+      <c r="D100" t="s">
         <v>3135</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-      <c r="B101" s="21" t="s">
+      <c r="B101" t="s">
         <v>2900</v>
       </c>
-      <c r="C101" s="21" t="s">
+      <c r="C101" t="s">
         <v>2901</v>
       </c>
-      <c r="D101" s="22" t="s">
+      <c r="D101" t="s">
         <v>3119</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
-      <c r="B102" s="21" t="s">
+      <c r="B102" t="s">
         <v>2902</v>
       </c>
-      <c r="C102" s="21" t="s">
+      <c r="C102" t="s">
         <v>2903</v>
       </c>
-      <c r="D102" s="22" t="s">
+      <c r="D102" t="s">
         <v>3110</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="B103" s="21" t="s">
+      <c r="B103" t="s">
         <v>2904</v>
       </c>
-      <c r="C103" s="21" t="s">
+      <c r="C103" t="s">
         <v>2905</v>
       </c>
-      <c r="D103" s="22" t="s">
+      <c r="D103" t="s">
         <v>3101</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <f t="shared" si="1"/>
         <v>101</v>
       </c>
-      <c r="B104" s="21" t="s">
+      <c r="B104" t="s">
         <v>2906</v>
       </c>
-      <c r="C104" s="21" t="s">
+      <c r="C104" t="s">
         <v>2907</v>
       </c>
-      <c r="D104" s="22" t="s">
+      <c r="D104" t="s">
         <v>3114</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <f t="shared" si="1"/>
         <v>102</v>
       </c>
-      <c r="B105" s="21" t="s">
+      <c r="B105" t="s">
         <v>2908</v>
       </c>
-      <c r="C105" s="21" t="s">
+      <c r="C105" t="s">
         <v>2909</v>
       </c>
-      <c r="D105" s="22" t="s">
+      <c r="D105" t="s">
         <v>3101</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <f t="shared" si="1"/>
         <v>103</v>
       </c>
-      <c r="B106" s="21" t="s">
+      <c r="B106" t="s">
         <v>1253</v>
       </c>
-      <c r="C106" s="21" t="s">
+      <c r="C106" t="s">
         <v>1254</v>
       </c>
-      <c r="D106" s="22" t="s">
+      <c r="D106" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <f t="shared" si="1"/>
         <v>104</v>
       </c>
-      <c r="B107" s="21" t="s">
+      <c r="B107" t="s">
         <v>2910</v>
       </c>
-      <c r="C107" s="21" t="s">
+      <c r="C107" t="s">
         <v>2911</v>
       </c>
-      <c r="D107" s="22" t="s">
+      <c r="D107" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <f t="shared" si="1"/>
         <v>105</v>
       </c>
-      <c r="B108" s="21" t="s">
+      <c r="B108" t="s">
         <v>2912</v>
       </c>
-      <c r="C108" s="21" t="s">
+      <c r="C108" t="s">
         <v>2913</v>
       </c>
-      <c r="D108" s="22" t="s">
+      <c r="D108" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <f t="shared" si="1"/>
         <v>106</v>
       </c>
-      <c r="B109" s="21" t="s">
+      <c r="B109" t="s">
         <v>2914</v>
       </c>
-      <c r="C109" s="21" t="s">
+      <c r="C109" t="s">
         <v>2915</v>
       </c>
-      <c r="D109" s="22" t="s">
+      <c r="D109" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <f t="shared" si="1"/>
         <v>107</v>
       </c>
-      <c r="B110" s="21" t="s">
+      <c r="B110" t="s">
         <v>2916</v>
       </c>
-      <c r="C110" s="21" t="s">
+      <c r="C110" t="s">
         <v>2917</v>
       </c>
-      <c r="D110" s="22" t="s">
+      <c r="D110" t="s">
         <v>3136</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <f t="shared" si="1"/>
         <v>108</v>
       </c>
-      <c r="B111" s="21" t="s">
+      <c r="B111" t="s">
         <v>2918</v>
       </c>
-      <c r="C111" s="21" t="s">
+      <c r="C111" t="s">
         <v>2919</v>
       </c>
-      <c r="D111" s="22" t="s">
+      <c r="D111" t="s">
         <v>3119</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <f t="shared" si="1"/>
         <v>109</v>
       </c>
-      <c r="B112" s="21" t="s">
+      <c r="B112" t="s">
         <v>2920</v>
       </c>
-      <c r="C112" s="21" t="s">
+      <c r="C112" t="s">
         <v>2921</v>
       </c>
-      <c r="D112" s="22" t="s">
+      <c r="D112" t="s">
         <v>3124</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
-      <c r="B113" s="21" t="s">
+      <c r="B113" t="s">
         <v>2922</v>
       </c>
-      <c r="C113" s="21" t="s">
+      <c r="C113" t="s">
         <v>2923</v>
       </c>
-      <c r="D113" s="22" t="s">
+      <c r="D113" t="s">
         <v>3128</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <f t="shared" si="1"/>
         <v>111</v>
       </c>
-      <c r="B114" s="21" t="s">
+      <c r="B114" t="s">
         <v>2924</v>
       </c>
-      <c r="C114" s="21" t="s">
+      <c r="C114" t="s">
         <v>2925</v>
       </c>
-      <c r="D114" s="22" t="s">
+      <c r="D114" t="s">
         <v>3137</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <f t="shared" si="1"/>
         <v>112</v>
       </c>
-      <c r="B115" s="21" t="s">
+      <c r="B115" t="s">
         <v>2926</v>
       </c>
-      <c r="C115" s="21" t="s">
+      <c r="C115" t="s">
         <v>2927</v>
       </c>
-      <c r="D115" s="22" t="s">
+      <c r="D115" t="s">
         <v>3106</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <f t="shared" si="1"/>
         <v>113</v>
       </c>
-      <c r="B116" s="21" t="s">
+      <c r="B116" t="s">
         <v>2928</v>
       </c>
-      <c r="C116" s="21" t="s">
+      <c r="C116" t="s">
         <v>2929</v>
       </c>
-      <c r="D116" s="22" t="s">
+      <c r="D116" t="s">
         <v>3138</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <f t="shared" si="1"/>
         <v>114</v>
       </c>
-      <c r="B117" s="21" t="s">
+      <c r="B117" t="s">
         <v>2930</v>
       </c>
-      <c r="C117" s="21" t="s">
+      <c r="C117" t="s">
         <v>2931</v>
       </c>
-      <c r="D117" s="22" t="s">
+      <c r="D117" t="s">
         <v>3111</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <f t="shared" si="1"/>
         <v>115</v>
       </c>
-      <c r="B118" s="21" t="s">
+      <c r="B118" t="s">
         <v>2932</v>
       </c>
-      <c r="C118" s="21" t="s">
+      <c r="C118" t="s">
         <v>2933</v>
       </c>
-      <c r="D118" s="22" t="s">
+      <c r="D118" t="s">
         <v>3122</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <f t="shared" si="1"/>
         <v>116</v>
       </c>
-      <c r="B119" s="21" t="s">
+      <c r="B119" t="s">
         <v>2934</v>
       </c>
-      <c r="C119" s="21" t="s">
+      <c r="C119" t="s">
         <v>2935</v>
       </c>
-      <c r="D119" s="22" t="s">
+      <c r="D119" t="s">
         <v>3119</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <f t="shared" si="1"/>
         <v>117</v>
       </c>
-      <c r="B120" s="21" t="s">
+      <c r="B120" t="s">
         <v>2936</v>
       </c>
-      <c r="C120" s="21" t="s">
+      <c r="C120" t="s">
         <v>2937</v>
       </c>
-      <c r="D120" s="22" t="s">
+      <c r="D120" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F120" s="4"/>
+      <c r="G120" s="4"/>
+      <c r="H120" s="4"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <f t="shared" si="1"/>
         <v>118</v>
       </c>
-      <c r="B121" s="21" t="s">
+      <c r="B121" t="s">
         <v>2938</v>
       </c>
-      <c r="C121" s="21" t="s">
+      <c r="C121" t="s">
         <v>2939</v>
       </c>
-      <c r="D121" s="22" t="s">
+      <c r="D121" t="s">
         <v>3105</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F121" s="4"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <f t="shared" si="1"/>
         <v>119</v>
       </c>
-      <c r="B122" s="21" t="s">
+      <c r="B122" t="s">
         <v>2940</v>
       </c>
-      <c r="C122" s="21" t="s">
+      <c r="C122" t="s">
         <v>2941</v>
       </c>
-      <c r="D122" s="22" t="s">
+      <c r="D122" t="s">
         <v>3119</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F122" s="4"/>
+      <c r="G122" s="4"/>
+      <c r="H122" s="4"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="B123" s="21" t="s">
+      <c r="B123" t="s">
         <v>2942</v>
       </c>
-      <c r="C123" s="21" t="s">
+      <c r="C123" t="s">
         <v>2943</v>
       </c>
-      <c r="D123" s="22" t="s">
+      <c r="D123" t="s">
         <v>3138</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="4"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <f t="shared" si="1"/>
         <v>121</v>
       </c>
-      <c r="B124" s="21" t="s">
+      <c r="B124" t="s">
         <v>2944</v>
       </c>
-      <c r="C124" s="21" t="s">
+      <c r="C124" t="s">
         <v>2945</v>
       </c>
-      <c r="D124" s="22" t="s">
+      <c r="D124" t="s">
         <v>3104</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F124" s="4"/>
+      <c r="G124" s="4"/>
+      <c r="H124" s="4"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <f t="shared" si="1"/>
         <v>122</v>
       </c>
-      <c r="B125" s="21" t="s">
+      <c r="B125" t="s">
         <v>2946</v>
       </c>
-      <c r="C125" s="21" t="s">
+      <c r="C125" t="s">
         <v>2947</v>
       </c>
-      <c r="D125" s="22" t="s">
+      <c r="D125" t="s">
         <v>3139</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F125" s="4"/>
+      <c r="G125" s="4"/>
+      <c r="H125" s="4"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <f t="shared" si="1"/>
         <v>123</v>
       </c>
-      <c r="B126" s="21" t="s">
+      <c r="B126" t="s">
         <v>2948</v>
       </c>
-      <c r="C126" s="21" t="s">
+      <c r="C126" t="s">
         <v>2949</v>
       </c>
-      <c r="D126" s="22" t="s">
+      <c r="D126" t="s">
         <v>3114</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F126" s="4"/>
+      <c r="G126" s="4"/>
+      <c r="H126" s="4"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <f t="shared" si="1"/>
         <v>124</v>
       </c>
-      <c r="B127" s="21" t="s">
+      <c r="B127" t="s">
         <v>2950</v>
       </c>
-      <c r="C127" s="21" t="s">
+      <c r="C127" t="s">
         <v>2951</v>
       </c>
-      <c r="D127" s="22" t="s">
+      <c r="D127" t="s">
         <v>3136</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F127" s="4"/>
+      <c r="G127" s="4"/>
+      <c r="H127" s="4"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <f t="shared" si="1"/>
         <v>125</v>
       </c>
-      <c r="B128" s="21" t="s">
+      <c r="B128" t="s">
         <v>2952</v>
       </c>
-      <c r="C128" s="21" t="s">
+      <c r="C128" t="s">
         <v>2953</v>
       </c>
-      <c r="D128" s="22" t="s">
+      <c r="D128" t="s">
         <v>3140</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F128" s="4"/>
+      <c r="G128" s="4"/>
+      <c r="H128" s="4"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <f t="shared" si="1"/>
         <v>126</v>
       </c>
-      <c r="B129" s="21" t="s">
+      <c r="B129" t="s">
         <v>2954</v>
       </c>
-      <c r="C129" s="21" t="s">
+      <c r="C129" t="s">
         <v>2955</v>
       </c>
-      <c r="D129" s="22" t="s">
+      <c r="D129" t="s">
         <v>3114</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F129" s="4"/>
+      <c r="G129" s="4"/>
+      <c r="H129" s="4"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <f t="shared" si="1"/>
         <v>127</v>
       </c>
-      <c r="B130" s="21" t="s">
+      <c r="B130" t="s">
         <v>2956</v>
       </c>
-      <c r="C130" s="21" t="s">
+      <c r="C130" t="s">
         <v>2957</v>
       </c>
-      <c r="D130" s="22" t="s">
+      <c r="D130" t="s">
         <v>3129</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F130" s="4"/>
+      <c r="G130" s="4"/>
+      <c r="H130" s="4"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <f t="shared" si="1"/>
         <v>128</v>
       </c>
-      <c r="B131" s="21" t="s">
+      <c r="B131" t="s">
         <v>2958</v>
       </c>
-      <c r="C131" s="21" t="s">
+      <c r="C131" t="s">
         <v>2959</v>
       </c>
-      <c r="D131" s="22" t="s">
+      <c r="D131" t="s">
         <v>3141</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F131" s="4"/>
+      <c r="G131" s="4"/>
+      <c r="H131" s="4"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <f t="shared" si="1"/>
         <v>129</v>
       </c>
-      <c r="B132" s="21" t="s">
+      <c r="B132" t="s">
         <v>2960</v>
       </c>
-      <c r="C132" s="21" t="s">
+      <c r="C132" t="s">
         <v>2961</v>
       </c>
-      <c r="D132" s="22" t="s">
+      <c r="D132" t="s">
         <v>3116</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F132" s="4"/>
+      <c r="G132" s="4"/>
+      <c r="H132" s="4"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <f t="shared" si="1"/>
         <v>130</v>
       </c>
-      <c r="B133" s="21" t="s">
+      <c r="B133" t="s">
         <v>2962</v>
       </c>
-      <c r="C133" s="21" t="s">
+      <c r="C133" t="s">
         <v>2963</v>
       </c>
-      <c r="D133" s="22" t="s">
+      <c r="D133" t="s">
         <v>3129</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F133" s="4"/>
+      <c r="G133" s="4"/>
+      <c r="H133" s="4"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <f t="shared" ref="A134:A197" si="2">+A133+1</f>
         <v>131</v>
       </c>
-      <c r="B134" s="21" t="s">
+      <c r="B134" t="s">
         <v>2964</v>
       </c>
-      <c r="C134" s="21" t="s">
+      <c r="C134" t="s">
         <v>2965</v>
       </c>
-      <c r="D134" s="22" t="s">
+      <c r="D134" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F134" s="4"/>
+      <c r="G134" s="4"/>
+      <c r="H134" s="4"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
-      <c r="B135" s="21" t="s">
+      <c r="B135" t="s">
         <v>1306</v>
       </c>
-      <c r="C135" s="21" t="s">
+      <c r="C135" t="s">
         <v>1307</v>
       </c>
-      <c r="D135" s="22" t="s">
+      <c r="D135" t="s">
         <v>3107</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F135" s="4"/>
+      <c r="G135" s="4"/>
+      <c r="H135" s="4"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
-      <c r="B136" s="21" t="s">
+      <c r="B136" t="s">
         <v>2966</v>
       </c>
-      <c r="C136" s="21" t="s">
+      <c r="C136" t="s">
         <v>2967</v>
       </c>
-      <c r="D136" s="22" t="s">
+      <c r="D136" t="s">
         <v>3134</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F136" s="4"/>
+      <c r="G136" s="4"/>
+      <c r="H136" s="4"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <f t="shared" si="2"/>
         <v>134</v>
       </c>
-      <c r="B137" s="21" t="s">
+      <c r="B137" t="s">
         <v>2968</v>
       </c>
-      <c r="C137" s="21" t="s">
+      <c r="C137" t="s">
         <v>2969</v>
       </c>
-      <c r="D137" s="22" t="s">
+      <c r="D137" t="s">
         <v>3107</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F137" s="4"/>
+      <c r="G137" s="4"/>
+      <c r="H137" s="4"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <f t="shared" si="2"/>
         <v>135</v>
       </c>
-      <c r="B138" s="21" t="s">
+      <c r="B138" t="s">
         <v>2970</v>
       </c>
-      <c r="C138" s="21" t="s">
+      <c r="C138" t="s">
         <v>2971</v>
       </c>
-      <c r="D138" s="22" t="s">
+      <c r="D138" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F138" s="4"/>
+      <c r="G138" s="4"/>
+      <c r="H138" s="4"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <f t="shared" si="2"/>
         <v>136</v>
       </c>
-      <c r="B139" s="21" t="s">
+      <c r="B139" t="s">
         <v>2972</v>
       </c>
-      <c r="C139" s="21" t="s">
+      <c r="C139" t="s">
         <v>2973</v>
       </c>
-      <c r="D139" s="22" t="s">
+      <c r="D139" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F139" s="4"/>
+      <c r="G139" s="4"/>
+      <c r="H139" s="4"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <f t="shared" si="2"/>
         <v>137</v>
       </c>
-      <c r="B140" s="21" t="s">
+      <c r="B140" t="s">
         <v>2974</v>
       </c>
-      <c r="C140" s="21" t="s">
+      <c r="C140" t="s">
         <v>2975</v>
       </c>
-      <c r="D140" s="22" t="s">
+      <c r="D140" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F140" s="4"/>
+      <c r="G140" s="4"/>
+      <c r="H140" s="4"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <f t="shared" si="2"/>
         <v>138</v>
       </c>
-      <c r="B141" s="21" t="s">
+      <c r="B141" t="s">
         <v>2976</v>
       </c>
-      <c r="C141" s="21" t="s">
+      <c r="C141" t="s">
         <v>2977</v>
       </c>
-      <c r="D141" s="22" t="s">
+      <c r="D141" t="s">
         <v>3134</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F141" s="4"/>
+      <c r="G141" s="4"/>
+      <c r="H141" s="4"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <f t="shared" si="2"/>
         <v>139</v>
       </c>
-      <c r="B142" s="21" t="s">
+      <c r="B142" t="s">
         <v>2978</v>
       </c>
-      <c r="C142" s="21" t="s">
+      <c r="C142" t="s">
         <v>2979</v>
       </c>
-      <c r="D142" s="22" t="s">
+      <c r="D142" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F142" s="4"/>
+      <c r="G142" s="4"/>
+      <c r="H142" s="4"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
         <f t="shared" si="2"/>
         <v>140</v>
       </c>
-      <c r="B143" s="21" t="s">
+      <c r="B143" t="s">
         <v>2980</v>
       </c>
-      <c r="C143" s="21" t="s">
+      <c r="C143" t="s">
         <v>2981</v>
       </c>
-      <c r="D143" s="22" t="s">
+      <c r="D143" t="s">
         <v>3121</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F143" s="4"/>
+      <c r="G143" s="4"/>
+      <c r="H143" s="4"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <f t="shared" si="2"/>
         <v>141</v>
       </c>
-      <c r="B144" s="21" t="s">
+      <c r="B144" t="s">
         <v>2982</v>
       </c>
-      <c r="C144" s="21" t="s">
+      <c r="C144" t="s">
         <v>2983</v>
       </c>
-      <c r="D144" s="22" t="s">
+      <c r="D144" t="s">
         <v>3108</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F144" s="4"/>
+      <c r="G144" s="4"/>
+      <c r="H144" s="4"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <f t="shared" si="2"/>
         <v>142</v>
       </c>
-      <c r="B145" s="21" t="s">
+      <c r="B145" t="s">
         <v>2984</v>
       </c>
-      <c r="C145" s="21" t="s">
+      <c r="C145" t="s">
         <v>2985</v>
       </c>
-      <c r="D145" s="22" t="s">
+      <c r="D145" t="s">
         <v>3114</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F145" s="4"/>
+      <c r="G145" s="4"/>
+      <c r="H145" s="4"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <f t="shared" si="2"/>
         <v>143</v>
       </c>
-      <c r="B146" s="21" t="s">
+      <c r="B146" t="s">
         <v>2986</v>
       </c>
-      <c r="C146" s="21" t="s">
+      <c r="C146" t="s">
         <v>2987</v>
       </c>
-      <c r="D146" s="22" t="s">
+      <c r="D146" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F146" s="4"/>
+      <c r="G146" s="4"/>
+      <c r="H146" s="4"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <f t="shared" si="2"/>
         <v>144</v>
       </c>
-      <c r="B147" s="21" t="s">
+      <c r="B147" t="s">
         <v>2988</v>
       </c>
-      <c r="C147" s="21" t="s">
+      <c r="C147" t="s">
         <v>2989</v>
       </c>
-      <c r="D147" s="22" t="s">
+      <c r="D147" t="s">
         <v>3101</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F147" s="4"/>
+      <c r="G147" s="4"/>
+      <c r="H147" s="4"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <f t="shared" si="2"/>
         <v>145</v>
       </c>
-      <c r="B148" s="21" t="s">
+      <c r="B148" t="s">
         <v>1366</v>
       </c>
-      <c r="C148" s="21" t="s">
+      <c r="C148" t="s">
         <v>1367</v>
       </c>
-      <c r="D148" s="22" t="s">
+      <c r="D148" t="s">
         <v>3107</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F148" s="4"/>
+      <c r="G148" s="4"/>
+      <c r="H148" s="4"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <f t="shared" si="2"/>
         <v>146</v>
       </c>
-      <c r="B149" s="21" t="s">
+      <c r="B149" t="s">
         <v>2990</v>
       </c>
-      <c r="C149" s="21" t="s">
+      <c r="C149" t="s">
         <v>2991</v>
       </c>
-      <c r="D149" s="22" t="s">
+      <c r="D149" t="s">
         <v>3142</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F149" s="4"/>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <f t="shared" si="2"/>
         <v>147</v>
       </c>
-      <c r="B150" s="21" t="s">
+      <c r="B150" t="s">
         <v>2992</v>
       </c>
-      <c r="C150" s="21" t="s">
+      <c r="C150" t="s">
         <v>2993</v>
       </c>
-      <c r="D150" s="22" t="s">
+      <c r="D150" t="s">
         <v>3143</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F150" s="4"/>
+      <c r="G150" s="4"/>
+      <c r="H150" s="4"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <f t="shared" si="2"/>
         <v>148</v>
       </c>
-      <c r="B151" s="21" t="s">
+      <c r="B151" t="s">
         <v>2994</v>
       </c>
-      <c r="C151" s="21" t="s">
+      <c r="C151" t="s">
         <v>2995</v>
       </c>
-      <c r="D151" s="22" t="s">
+      <c r="D151" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F151" s="4"/>
+      <c r="G151" s="4"/>
+      <c r="H151" s="4"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <f t="shared" si="2"/>
         <v>149</v>
       </c>
-      <c r="B152" s="21" t="s">
+      <c r="B152" t="s">
         <v>2996</v>
       </c>
-      <c r="C152" s="21" t="s">
+      <c r="C152" t="s">
         <v>2997</v>
       </c>
-      <c r="D152" s="22" t="s">
+      <c r="D152" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F152" s="4"/>
+      <c r="G152" s="4"/>
+      <c r="H152" s="4"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
-      <c r="B153" s="21" t="s">
+      <c r="B153" t="s">
         <v>2998</v>
       </c>
-      <c r="C153" s="21" t="s">
+      <c r="C153" t="s">
         <v>2999</v>
       </c>
-      <c r="D153" s="22" t="s">
+      <c r="D153" t="s">
         <v>3111</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F153" s="4"/>
+      <c r="G153" s="4"/>
+      <c r="H153" s="4"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <f t="shared" si="2"/>
         <v>151</v>
       </c>
-      <c r="B154" s="21" t="s">
+      <c r="B154" t="s">
         <v>3000</v>
       </c>
-      <c r="C154" s="21" t="s">
+      <c r="C154" t="s">
         <v>3001</v>
       </c>
-      <c r="D154" s="22" t="s">
+      <c r="D154" t="s">
         <v>3111</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F154" s="4"/>
+      <c r="G154" s="4"/>
+      <c r="H154" s="4"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <f t="shared" si="2"/>
         <v>152</v>
       </c>
-      <c r="B155" s="21" t="s">
+      <c r="B155" t="s">
         <v>3002</v>
       </c>
-      <c r="C155" s="21" t="s">
+      <c r="C155" t="s">
         <v>3003</v>
       </c>
-      <c r="D155" s="22" t="s">
+      <c r="D155" t="s">
         <v>3130</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F155" s="4"/>
+      <c r="G155" s="4"/>
+      <c r="H155" s="4"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <f t="shared" si="2"/>
         <v>153</v>
       </c>
-      <c r="B156" s="21" t="s">
+      <c r="B156" t="s">
         <v>1616</v>
       </c>
-      <c r="C156" s="21" t="s">
+      <c r="C156" t="s">
         <v>1617</v>
       </c>
-      <c r="D156" s="22" t="s">
+      <c r="D156" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F156" s="4"/>
+      <c r="G156" s="4"/>
+      <c r="H156" s="4"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <f t="shared" si="2"/>
         <v>154</v>
       </c>
-      <c r="B157" s="21" t="s">
+      <c r="B157" t="s">
         <v>3004</v>
       </c>
-      <c r="C157" s="21" t="s">
+      <c r="C157" t="s">
         <v>3005</v>
       </c>
-      <c r="D157" s="22" t="s">
+      <c r="D157" t="s">
         <v>3105</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F157" s="4"/>
+      <c r="G157" s="4"/>
+      <c r="H157" s="4"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <f t="shared" si="2"/>
         <v>155</v>
       </c>
-      <c r="B158" s="21" t="s">
+      <c r="B158" t="s">
         <v>3006</v>
       </c>
-      <c r="C158" s="21" t="s">
+      <c r="C158" t="s">
         <v>3007</v>
       </c>
-      <c r="D158" s="22" t="s">
+      <c r="D158" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F158" s="4"/>
+      <c r="G158" s="4"/>
+      <c r="H158" s="4"/>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
         <f t="shared" si="2"/>
         <v>156</v>
       </c>
-      <c r="B159" s="21" t="s">
+      <c r="B159" t="s">
         <v>3008</v>
       </c>
-      <c r="C159" s="21" t="s">
+      <c r="C159" t="s">
         <v>3009</v>
       </c>
-      <c r="D159" s="22" t="s">
+      <c r="D159" t="s">
         <v>3117</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F159" s="4"/>
+      <c r="G159" s="4"/>
+      <c r="H159" s="4"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
         <f t="shared" si="2"/>
         <v>157</v>
       </c>
-      <c r="B160" s="21" t="s">
+      <c r="B160" t="s">
         <v>3010</v>
       </c>
-      <c r="C160" s="21" t="s">
+      <c r="C160" t="s">
         <v>3011</v>
       </c>
-      <c r="D160" s="22" t="s">
+      <c r="D160" t="s">
         <v>3122</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F160" s="4"/>
+      <c r="G160" s="4"/>
+      <c r="H160" s="4"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
         <f t="shared" si="2"/>
         <v>158</v>
       </c>
-      <c r="B161" s="21" t="s">
+      <c r="B161" t="s">
         <v>3012</v>
       </c>
-      <c r="C161" s="21" t="s">
+      <c r="C161" t="s">
         <v>3013</v>
       </c>
-      <c r="D161" s="22" t="s">
+      <c r="D161" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F161" s="4"/>
+      <c r="G161" s="4"/>
+      <c r="H161" s="4"/>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <f t="shared" si="2"/>
         <v>159</v>
       </c>
-      <c r="B162" s="21" t="s">
+      <c r="B162" t="s">
         <v>3014</v>
       </c>
-      <c r="C162" s="21" t="s">
+      <c r="C162" t="s">
         <v>3015</v>
       </c>
-      <c r="D162" s="22" t="s">
+      <c r="D162" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F162" s="4"/>
+      <c r="G162" s="4"/>
+      <c r="H162" s="4"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
         <f t="shared" si="2"/>
         <v>160</v>
       </c>
-      <c r="B163" s="21" t="s">
+      <c r="B163" t="s">
         <v>3016</v>
       </c>
-      <c r="C163" s="21" t="s">
+      <c r="C163" t="s">
         <v>3017</v>
       </c>
-      <c r="D163" s="22" t="s">
+      <c r="D163" t="s">
         <v>3109</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F163" s="4"/>
+      <c r="G163" s="4"/>
+      <c r="H163" s="4"/>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
         <f t="shared" si="2"/>
         <v>161</v>
       </c>
-      <c r="B164" s="21" t="s">
+      <c r="B164" t="s">
         <v>3018</v>
       </c>
-      <c r="C164" s="21" t="s">
+      <c r="C164" t="s">
         <v>3019</v>
       </c>
-      <c r="D164" s="22" t="s">
+      <c r="D164" t="s">
         <v>3134</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F164" s="4"/>
+      <c r="G164" s="4"/>
+      <c r="H164" s="4"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
         <f t="shared" si="2"/>
         <v>162</v>
       </c>
-      <c r="B165" s="21" t="s">
+      <c r="B165" t="s">
         <v>3020</v>
       </c>
-      <c r="C165" s="21" t="s">
+      <c r="C165" t="s">
         <v>3021</v>
       </c>
-      <c r="D165" s="22" t="s">
+      <c r="D165" t="s">
         <v>3109</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F165" s="4"/>
+      <c r="G165" s="4"/>
+      <c r="H165" s="4"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
         <f t="shared" si="2"/>
         <v>163</v>
       </c>
-      <c r="B166" s="21" t="s">
+      <c r="B166" t="s">
         <v>3022</v>
       </c>
-      <c r="C166" s="21" t="s">
+      <c r="C166" t="s">
         <v>3023</v>
       </c>
-      <c r="D166" s="22" t="s">
+      <c r="D166" t="s">
         <v>3102</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F166" s="4"/>
+      <c r="G166" s="4"/>
+      <c r="H166" s="4"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <f t="shared" si="2"/>
         <v>164</v>
       </c>
-      <c r="B167" s="21" t="s">
+      <c r="B167" t="s">
         <v>3024</v>
       </c>
-      <c r="C167" s="21" t="s">
+      <c r="C167" t="s">
         <v>3025</v>
       </c>
-      <c r="D167" s="22" t="s">
+      <c r="D167" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F167" s="4"/>
+      <c r="G167" s="4"/>
+      <c r="H167" s="4"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
         <f t="shared" si="2"/>
         <v>165</v>
       </c>
-      <c r="B168" s="21" t="s">
+      <c r="B168" t="s">
         <v>3026</v>
       </c>
-      <c r="C168" s="21" t="s">
+      <c r="C168" t="s">
         <v>3027</v>
       </c>
-      <c r="D168" s="22" t="s">
+      <c r="D168" t="s">
         <v>3110</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F168" s="4"/>
+      <c r="G168" s="4"/>
+      <c r="H168" s="4"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <f t="shared" si="2"/>
         <v>166</v>
       </c>
-      <c r="B169" s="21" t="s">
+      <c r="B169" t="s">
         <v>3028</v>
       </c>
-      <c r="C169" s="21" t="s">
+      <c r="C169" t="s">
         <v>3029</v>
       </c>
-      <c r="D169" s="22" t="s">
+      <c r="D169" t="s">
         <v>3134</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F169" s="4"/>
+      <c r="G169" s="4"/>
+      <c r="H169" s="4"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="5">
         <f t="shared" si="2"/>
         <v>167</v>
       </c>
-      <c r="B170" s="21" t="s">
+      <c r="B170" t="s">
         <v>3030</v>
       </c>
-      <c r="C170" s="21" t="s">
+      <c r="C170" t="s">
         <v>3031</v>
       </c>
-      <c r="D170" s="22" t="s">
+      <c r="D170" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F170" s="4"/>
+      <c r="G170" s="4"/>
+      <c r="H170" s="4"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <f t="shared" si="2"/>
         <v>168</v>
       </c>
-      <c r="B171" s="21" t="s">
+      <c r="B171" t="s">
         <v>3032</v>
       </c>
-      <c r="C171" s="21" t="s">
+      <c r="C171" t="s">
         <v>3033</v>
       </c>
-      <c r="D171" s="22" t="s">
+      <c r="D171" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F171" s="4"/>
+      <c r="G171" s="4"/>
+      <c r="H171" s="4"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <f t="shared" si="2"/>
         <v>169</v>
       </c>
-      <c r="B172" s="21" t="s">
+      <c r="B172" t="s">
         <v>3034</v>
       </c>
-      <c r="C172" s="21" t="s">
+      <c r="C172" t="s">
         <v>3035</v>
       </c>
-      <c r="D172" s="22" t="s">
+      <c r="D172" t="s">
         <v>3141</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F172" s="4"/>
+      <c r="G172" s="4"/>
+      <c r="H172" s="4"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <f t="shared" si="2"/>
         <v>170</v>
       </c>
-      <c r="B173" s="21" t="s">
+      <c r="B173" t="s">
         <v>3036</v>
       </c>
-      <c r="C173" s="21" t="s">
+      <c r="C173" t="s">
         <v>3037</v>
       </c>
-      <c r="D173" s="22" t="s">
+      <c r="D173" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F173" s="4"/>
+      <c r="G173" s="4"/>
+      <c r="H173" s="4"/>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <f t="shared" si="2"/>
         <v>171</v>
       </c>
-      <c r="B174" s="21" t="s">
+      <c r="B174" t="s">
         <v>1883</v>
       </c>
-      <c r="C174" s="21" t="s">
+      <c r="C174" t="s">
         <v>1884</v>
       </c>
-      <c r="D174" s="22" t="s">
+      <c r="D174" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F174" s="4"/>
+      <c r="G174" s="4"/>
+      <c r="H174" s="4"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
         <f t="shared" si="2"/>
         <v>172</v>
       </c>
-      <c r="B175" s="21" t="s">
+      <c r="B175" t="s">
         <v>3038</v>
       </c>
-      <c r="C175" s="21" t="s">
+      <c r="C175" t="s">
         <v>3039</v>
       </c>
-      <c r="D175" s="22" t="s">
+      <c r="D175" t="s">
         <v>1642</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F175" s="4"/>
+      <c r="G175" s="4"/>
+      <c r="H175" s="4"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="5">
         <f t="shared" si="2"/>
         <v>173</v>
       </c>
-      <c r="B176" s="21" t="s">
+      <c r="B176" t="s">
         <v>3040</v>
       </c>
-      <c r="C176" s="21" t="s">
+      <c r="C176" t="s">
         <v>3041</v>
       </c>
-      <c r="D176" s="22" t="s">
+      <c r="D176" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F176" s="4"/>
+      <c r="G176" s="4"/>
+      <c r="H176" s="4"/>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="5">
         <f t="shared" si="2"/>
         <v>174</v>
       </c>
-      <c r="B177" s="21" t="s">
+      <c r="B177" t="s">
         <v>3042</v>
       </c>
-      <c r="C177" s="21" t="s">
+      <c r="C177" t="s">
         <v>3043</v>
       </c>
-      <c r="D177" s="22" t="s">
+      <c r="D177" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F177" s="4"/>
+      <c r="G177" s="4"/>
+      <c r="H177" s="4"/>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="5">
         <f t="shared" si="2"/>
         <v>175</v>
       </c>
-      <c r="B178" s="21" t="s">
+      <c r="B178" t="s">
         <v>3044</v>
       </c>
-      <c r="C178" s="21" t="s">
+      <c r="C178" t="s">
         <v>3045</v>
       </c>
-      <c r="D178" s="22" t="s">
+      <c r="D178" t="s">
         <v>3122</v>
       </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F178" s="4"/>
+      <c r="G178" s="4"/>
+      <c r="H178" s="4"/>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="5">
         <f t="shared" si="2"/>
         <v>176</v>
       </c>
-      <c r="B179" s="21" t="s">
+      <c r="B179" t="s">
         <v>3046</v>
       </c>
-      <c r="C179" s="21" t="s">
+      <c r="C179" t="s">
         <v>3047</v>
       </c>
-      <c r="D179" s="22" t="s">
+      <c r="D179" t="s">
         <v>3134</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F179" s="4"/>
+      <c r="G179" s="4"/>
+      <c r="H179" s="4"/>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="5">
         <f t="shared" si="2"/>
         <v>177</v>
       </c>
-      <c r="B180" s="21" t="s">
+      <c r="B180" t="s">
         <v>3048</v>
       </c>
-      <c r="C180" s="21" t="s">
+      <c r="C180" t="s">
         <v>3049</v>
       </c>
-      <c r="D180" s="22" t="s">
+      <c r="D180" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F180" s="4"/>
+      <c r="G180" s="4"/>
+      <c r="H180" s="4"/>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="5">
         <f t="shared" si="2"/>
         <v>178</v>
       </c>
-      <c r="B181" s="21" t="s">
+      <c r="B181" t="s">
         <v>3050</v>
       </c>
-      <c r="C181" s="21" t="s">
+      <c r="C181" t="s">
         <v>3051</v>
       </c>
-      <c r="D181" s="22" t="s">
+      <c r="D181" t="s">
         <v>3111</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F181" s="4"/>
+      <c r="G181" s="4"/>
+      <c r="H181" s="4"/>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="5">
         <f t="shared" si="2"/>
         <v>179</v>
       </c>
-      <c r="B182" s="21" t="s">
+      <c r="B182" t="s">
         <v>3052</v>
       </c>
-      <c r="C182" s="21" t="s">
+      <c r="C182" t="s">
         <v>3053</v>
       </c>
-      <c r="D182" s="22" t="s">
+      <c r="D182" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F182" s="4"/>
+      <c r="G182" s="4"/>
+      <c r="H182" s="4"/>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="5">
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
-      <c r="B183" s="21" t="s">
+      <c r="B183" t="s">
         <v>3054</v>
       </c>
-      <c r="C183" s="21" t="s">
+      <c r="C183" t="s">
         <v>3055</v>
       </c>
-      <c r="D183" s="22" t="s">
+      <c r="D183" t="s">
         <v>3144</v>
       </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F183" s="4"/>
+      <c r="G183" s="4"/>
+      <c r="H183" s="4"/>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="5">
         <f t="shared" si="2"/>
         <v>181</v>
       </c>
-      <c r="B184" s="21" t="s">
+      <c r="B184" t="s">
         <v>3056</v>
       </c>
-      <c r="C184" s="21" t="s">
+      <c r="C184" t="s">
         <v>3057</v>
       </c>
-      <c r="D184" s="22" t="s">
+      <c r="D184" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F184" s="4"/>
+      <c r="G184" s="4"/>
+      <c r="H184" s="4"/>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="5">
         <f t="shared" si="2"/>
         <v>182</v>
       </c>
-      <c r="B185" s="21" t="s">
+      <c r="B185" t="s">
         <v>3058</v>
       </c>
-      <c r="C185" s="21" t="s">
+      <c r="C185" t="s">
         <v>3059</v>
       </c>
-      <c r="D185" s="22" t="s">
+      <c r="D185" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F185" s="4"/>
+      <c r="G185" s="4"/>
+      <c r="H185" s="4"/>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="5">
         <f t="shared" si="2"/>
         <v>183</v>
       </c>
-      <c r="B186" s="21" t="s">
+      <c r="B186" t="s">
         <v>3060</v>
       </c>
-      <c r="C186" s="21" t="s">
+      <c r="C186" t="s">
         <v>3061</v>
       </c>
-      <c r="D186" s="22" t="s">
+      <c r="D186" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F186" s="4"/>
+      <c r="G186" s="4"/>
+      <c r="H186" s="4"/>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="5">
         <f t="shared" si="2"/>
         <v>184</v>
       </c>
-      <c r="B187" s="21" t="s">
+      <c r="B187" t="s">
         <v>3062</v>
       </c>
-      <c r="C187" s="21" t="s">
+      <c r="C187" t="s">
         <v>3063</v>
       </c>
-      <c r="D187" s="22" t="s">
+      <c r="D187" t="s">
         <v>3134</v>
       </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F187" s="4"/>
+      <c r="G187" s="4"/>
+      <c r="H187" s="4"/>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="5">
         <f t="shared" si="2"/>
         <v>185</v>
       </c>
-      <c r="B188" s="21" t="s">
+      <c r="B188" t="s">
         <v>3064</v>
       </c>
-      <c r="C188" s="21" t="s">
+      <c r="C188" t="s">
         <v>3065</v>
       </c>
-      <c r="D188" s="22" t="s">
+      <c r="D188" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F188" s="4"/>
+      <c r="G188" s="4"/>
+      <c r="H188" s="4"/>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="5">
         <f t="shared" si="2"/>
         <v>186</v>
       </c>
-      <c r="B189" s="21" t="s">
+      <c r="B189" t="s">
         <v>3066</v>
       </c>
-      <c r="C189" s="21" t="s">
+      <c r="C189" t="s">
         <v>3067</v>
       </c>
-      <c r="D189" s="22" t="s">
+      <c r="D189" t="s">
         <v>3110</v>
       </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F189" s="4"/>
+      <c r="G189" s="4"/>
+      <c r="H189" s="4"/>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="5">
         <f t="shared" si="2"/>
         <v>187</v>
       </c>
-      <c r="B190" s="21" t="s">
+      <c r="B190" t="s">
         <v>3068</v>
       </c>
-      <c r="C190" s="21" t="s">
+      <c r="C190" t="s">
         <v>3069</v>
       </c>
-      <c r="D190" s="22" t="s">
+      <c r="D190" t="s">
         <v>3116</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F190" s="4"/>
+      <c r="G190" s="4"/>
+      <c r="H190" s="4"/>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="5">
         <f t="shared" si="2"/>
         <v>188</v>
       </c>
-      <c r="B191" s="21" t="s">
+      <c r="B191" t="s">
         <v>2060</v>
       </c>
-      <c r="C191" s="21" t="s">
+      <c r="C191" t="s">
         <v>2061</v>
       </c>
-      <c r="D191" s="22" t="s">
+      <c r="D191" t="s">
         <v>3116</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F191" s="4"/>
+      <c r="G191" s="4"/>
+      <c r="H191" s="4"/>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="5">
         <f t="shared" si="2"/>
         <v>189</v>
       </c>
-      <c r="B192" s="21" t="s">
+      <c r="B192" t="s">
         <v>3070</v>
       </c>
-      <c r="C192" s="21" t="s">
+      <c r="C192" t="s">
         <v>3071</v>
       </c>
-      <c r="D192" s="22" t="s">
+      <c r="D192" t="s">
         <v>3120</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F192" s="4"/>
+      <c r="G192" s="4"/>
+      <c r="H192" s="4"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="5">
         <f t="shared" si="2"/>
         <v>190</v>
       </c>
-      <c r="B193" s="21" t="s">
+      <c r="B193" t="s">
         <v>3072</v>
       </c>
-      <c r="C193" s="21" t="s">
+      <c r="C193" t="s">
         <v>3073</v>
       </c>
-      <c r="D193" s="22" t="s">
+      <c r="D193" t="s">
         <v>3123</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F193" s="4"/>
+      <c r="G193" s="4"/>
+      <c r="H193" s="4"/>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="5">
         <f t="shared" si="2"/>
         <v>191</v>
       </c>
-      <c r="B194" s="21" t="s">
+      <c r="B194" t="s">
         <v>3074</v>
       </c>
-      <c r="C194" s="21" t="s">
+      <c r="C194" t="s">
         <v>3075</v>
       </c>
-      <c r="D194" s="22" t="s">
+      <c r="D194" t="s">
         <v>3145</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F194" s="4"/>
+      <c r="G194" s="4"/>
+      <c r="H194" s="4"/>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="5">
         <f t="shared" si="2"/>
         <v>192</v>
       </c>
-      <c r="B195" s="21" t="s">
+      <c r="B195" t="s">
         <v>3076</v>
       </c>
-      <c r="C195" s="21" t="s">
+      <c r="C195" t="s">
         <v>3077</v>
       </c>
-      <c r="D195" s="22" t="s">
+      <c r="D195" t="s">
         <v>3117</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F195" s="4"/>
+      <c r="G195" s="4"/>
+      <c r="H195" s="4"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="5">
         <f t="shared" si="2"/>
         <v>193</v>
       </c>
-      <c r="B196" s="21" t="s">
+      <c r="B196" t="s">
         <v>3078</v>
       </c>
-      <c r="C196" s="21" t="s">
+      <c r="C196" t="s">
         <v>3079</v>
       </c>
-      <c r="D196" s="22" t="s">
+      <c r="D196" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F196" s="4"/>
+      <c r="G196" s="4"/>
+      <c r="H196" s="4"/>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="5">
         <f t="shared" si="2"/>
         <v>194</v>
       </c>
-      <c r="B197" s="21" t="s">
+      <c r="B197" t="s">
         <v>3080</v>
       </c>
-      <c r="C197" s="21" t="s">
+      <c r="C197" t="s">
         <v>3081</v>
       </c>
-      <c r="D197" s="22" t="s">
+      <c r="D197" t="s">
         <v>3144</v>
       </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F197" s="4"/>
+      <c r="G197" s="4"/>
+      <c r="H197" s="4"/>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="5">
         <f t="shared" ref="A198:A223" si="3">+A197+1</f>
         <v>195</v>
       </c>
-      <c r="B198" s="21" t="s">
+      <c r="B198" t="s">
         <v>3082</v>
       </c>
-      <c r="C198" s="21" t="s">
+      <c r="C198" t="s">
         <v>3083</v>
       </c>
-      <c r="D198" s="22" t="s">
+      <c r="D198" t="s">
         <v>3101</v>
       </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F198" s="4"/>
+      <c r="G198" s="4"/>
+      <c r="H198" s="4"/>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="5">
         <f t="shared" si="3"/>
         <v>196</v>
       </c>
-      <c r="B199" s="21" t="s">
+      <c r="B199" t="s">
         <v>3084</v>
       </c>
-      <c r="C199" s="21" t="s">
+      <c r="C199" t="s">
         <v>3085</v>
       </c>
-      <c r="D199" s="22" t="s">
+      <c r="D199" t="s">
         <v>3109</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F199" s="4"/>
+      <c r="G199" s="4"/>
+      <c r="H199" s="4"/>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="5">
         <f t="shared" si="3"/>
         <v>197</v>
       </c>
-      <c r="B200" s="21" t="s">
+      <c r="B200" t="s">
         <v>2108</v>
       </c>
-      <c r="C200" s="21" t="s">
+      <c r="C200" t="s">
         <v>2109</v>
       </c>
-      <c r="D200" s="22" t="s">
+      <c r="D200" t="s">
         <v>3101</v>
       </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F200" s="4"/>
+      <c r="G200" s="4"/>
+      <c r="H200" s="4"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="5">
         <f t="shared" si="3"/>
         <v>198</v>
       </c>
-      <c r="B201" s="21" t="s">
+      <c r="B201" t="s">
         <v>2157</v>
       </c>
-      <c r="C201" s="21" t="s">
+      <c r="C201" t="s">
         <v>2158</v>
       </c>
-      <c r="D201" s="22" t="s">
+      <c r="D201" t="s">
         <v>3123</v>
       </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F201" s="4"/>
+      <c r="G201" s="4"/>
+      <c r="H201" s="4"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="5">
         <f t="shared" si="3"/>
         <v>199</v>
       </c>
-      <c r="B202" s="21" t="s">
+      <c r="B202" t="s">
         <v>3086</v>
       </c>
-      <c r="C202" s="21" t="s">
+      <c r="C202" t="s">
         <v>3087</v>
       </c>
-      <c r="D202" s="22" t="s">
+      <c r="D202" t="s">
         <v>3140</v>
       </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F202" s="4"/>
+      <c r="G202" s="4"/>
+      <c r="H202" s="4"/>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="5">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="B203" s="21" t="s">
+      <c r="B203" t="s">
         <v>2239</v>
       </c>
-      <c r="C203" s="21" t="s">
+      <c r="C203" t="s">
         <v>2240</v>
       </c>
-      <c r="D203" s="22" t="s">
+      <c r="D203" t="s">
         <v>3113</v>
       </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F203" s="4"/>
+      <c r="G203" s="4"/>
+      <c r="H203" s="4"/>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="5">
         <f t="shared" si="3"/>
         <v>201</v>
       </c>
-      <c r="B204" s="21" t="s">
+      <c r="B204" t="s">
         <v>3088</v>
       </c>
-      <c r="C204" s="21" t="s">
+      <c r="C204" t="s">
         <v>3089</v>
       </c>
-      <c r="D204" s="22" t="s">
+      <c r="D204" t="s">
         <v>3123</v>
       </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F204" s="4"/>
+      <c r="G204" s="4"/>
+      <c r="H204" s="4"/>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="5">
         <f t="shared" si="3"/>
         <v>202</v>
       </c>
-      <c r="B205" s="21" t="s">
+      <c r="B205" t="s">
         <v>3090</v>
       </c>
-      <c r="C205" s="21" t="s">
+      <c r="C205" t="s">
         <v>3091</v>
       </c>
-      <c r="D205" s="22" t="s">
+      <c r="D205" t="s">
         <v>3101</v>
       </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F205" s="4"/>
+      <c r="G205" s="4"/>
+      <c r="H205" s="4"/>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="5">
         <f t="shared" si="3"/>
         <v>203</v>
       </c>
-      <c r="B206" s="21" t="s">
+      <c r="B206" t="s">
         <v>3092</v>
       </c>
-      <c r="C206" s="21" t="s">
+      <c r="C206" t="s">
         <v>3093</v>
       </c>
-      <c r="D206" s="22" t="s">
+      <c r="D206" t="s">
         <v>3144</v>
       </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F206" s="4"/>
+      <c r="G206" s="4"/>
+      <c r="H206" s="4"/>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="5">
         <f t="shared" si="3"/>
         <v>204</v>
       </c>
-      <c r="B207" s="21" t="s">
+      <c r="B207" t="s">
         <v>3094</v>
       </c>
-      <c r="C207" s="21" t="s">
+      <c r="C207" t="s">
         <v>3095</v>
       </c>
-      <c r="D207" s="22" t="s">
+      <c r="D207" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F207" s="4"/>
+      <c r="G207" s="4"/>
+      <c r="H207" s="4"/>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="5">
         <f t="shared" si="3"/>
         <v>205</v>
       </c>
-      <c r="B208" s="21" t="s">
+      <c r="B208" t="s">
         <v>2356</v>
       </c>
-      <c r="C208" s="21" t="s">
+      <c r="C208" t="s">
         <v>2357</v>
       </c>
-      <c r="D208" s="22" t="s">
+      <c r="D208" t="s">
         <v>3134</v>
       </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F208" s="4"/>
+      <c r="G208" s="4"/>
+      <c r="H208" s="4"/>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="5">
         <f t="shared" si="3"/>
         <v>206</v>
       </c>
-      <c r="B209" s="21" t="s">
+      <c r="B209" t="s">
         <v>2456</v>
       </c>
-      <c r="C209" s="21" t="s">
+      <c r="C209" t="s">
         <v>2457</v>
       </c>
-      <c r="D209" s="22" t="s">
+      <c r="D209" t="s">
         <v>3103</v>
       </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F209" s="4"/>
+      <c r="G209" s="4"/>
+      <c r="H209" s="4"/>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="5">
         <f t="shared" si="3"/>
         <v>207</v>
       </c>
-      <c r="B210" s="21" t="s">
+      <c r="B210" t="s">
         <v>3096</v>
       </c>
-      <c r="C210" s="21" t="s">
+      <c r="C210" t="s">
         <v>3097</v>
       </c>
-      <c r="D210" s="22" t="s">
+      <c r="D210" t="s">
         <v>3099</v>
       </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F210" s="4"/>
+      <c r="G210" s="4"/>
+      <c r="H210" s="4"/>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="5">
         <f t="shared" si="3"/>
         <v>208</v>
       </c>
-      <c r="B211" s="21" t="s">
+      <c r="B211" t="s">
         <v>2486</v>
       </c>
-      <c r="C211" s="21" t="s">
+      <c r="C211" t="s">
         <v>3098</v>
       </c>
-      <c r="D211" s="22" t="s">
+      <c r="D211" t="s">
         <v>3101</v>
       </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F211" s="4"/>
+      <c r="G211" s="4"/>
+      <c r="H211" s="4"/>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="5">
         <f t="shared" si="3"/>
         <v>209</v>
       </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F212" s="4"/>
+      <c r="G212" s="4"/>
+      <c r="H212" s="4"/>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="5">
         <f t="shared" si="3"/>
         <v>210</v>
       </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F213" s="4"/>
+      <c r="G213" s="4"/>
+      <c r="H213" s="4"/>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="5">
         <f t="shared" si="3"/>
         <v>211</v>
       </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F214" s="4"/>
+      <c r="G214" s="4"/>
+      <c r="H214" s="4"/>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="5">
         <f t="shared" si="3"/>
         <v>212</v>
       </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F215" s="4"/>
+      <c r="G215" s="4"/>
+      <c r="H215" s="4"/>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="5">
         <f t="shared" si="3"/>
         <v>213</v>
       </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F216" s="4"/>
+      <c r="G216" s="4"/>
+      <c r="H216" s="4"/>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="5">
         <f t="shared" si="3"/>
         <v>214</v>
       </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F217" s="4"/>
+      <c r="G217" s="4"/>
+      <c r="H217" s="4"/>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="5">
         <f t="shared" si="3"/>
         <v>215</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="5">
         <f t="shared" si="3"/>
         <v>216</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="5">
         <f t="shared" si="3"/>
         <v>217</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="5">
         <f t="shared" si="3"/>
         <v>218</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="5">
         <f t="shared" si="3"/>
         <v>219</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="5">
         <f t="shared" si="3"/>
         <v>220</v>
@@ -38974,6 +39670,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{FEF2C0D4-AEE0-4A3F-A661-7994CD0FEC35}"/>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{3A0DAFC4-54CD-4959-8CC1-27C193A0828A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
